--- a/data/trans_dic/P38B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,79; 53,06</t>
+          <t>43,96; 53,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,74; 60,81</t>
+          <t>50,81; 60,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,11; 57,88</t>
+          <t>40,91; 58,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,6; 65,16</t>
+          <t>55,22; 64,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,14; 69,08</t>
+          <t>59,56; 68,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,87; 66,89</t>
+          <t>51,84; 66,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,29; 57,91</t>
+          <t>51,05; 57,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,68; 63,74</t>
+          <t>56,81; 63,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,97; 59,69</t>
+          <t>47,74; 59,55</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>73,16; 79,53</t>
+          <t>72,71; 79,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,4; 72,71</t>
+          <t>65,4; 72,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,62; 71,13</t>
+          <t>59,73; 71,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81,72; 87,74</t>
+          <t>82,13; 87,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,28; 84,43</t>
+          <t>78,29; 84,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,0; 78,47</t>
+          <t>39,9; 78,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,13; 82,73</t>
+          <t>78,19; 82,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,51; 77,78</t>
+          <t>72,99; 77,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,36; 72,88</t>
+          <t>47,93; 72,65</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,71; 87,92</t>
+          <t>82,4; 87,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,48; 84,74</t>
+          <t>78,55; 84,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,71; 80,44</t>
+          <t>73,2; 80,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,89; 92,52</t>
+          <t>87,76; 92,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,61; 88,2</t>
+          <t>82,67; 88,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,48; 86,81</t>
+          <t>82,09; 87,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,04; 89,65</t>
+          <t>85,95; 89,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,58; 85,43</t>
+          <t>81,24; 85,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78,56; 83,16</t>
+          <t>78,38; 82,84</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,57; 92,7</t>
+          <t>87,35; 92,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,97; 90,35</t>
+          <t>85,11; 90,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,67; 88,45</t>
+          <t>26,7; 88,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,0; 93,02</t>
+          <t>87,74; 92,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,99; 92,74</t>
+          <t>88,04; 92,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,24; 93,85</t>
+          <t>90,35; 93,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,7; 92,3</t>
+          <t>88,57; 92,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,28; 90,99</t>
+          <t>87,36; 91,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,57; 90,55</t>
+          <t>49,13; 90,55</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,48; 95,35</t>
+          <t>90,23; 95,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89,56; 94,65</t>
+          <t>89,33; 94,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,14; 94,4</t>
+          <t>90,32; 94,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92,5; 96,97</t>
+          <t>92,78; 97,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,11; 95,69</t>
+          <t>91,2; 95,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,94; 96,17</t>
+          <t>93,04; 96,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,59; 95,7</t>
+          <t>92,53; 95,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91,07; 94,59</t>
+          <t>90,66; 94,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,26; 95,11</t>
+          <t>92,39; 94,9</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,73; 98,34</t>
+          <t>93,29; 98,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,49; 99,05</t>
+          <t>95,25; 98,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,65; 97,24</t>
+          <t>93,67; 97,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,65; 97,19</t>
+          <t>92,63; 97,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>95,83; 98,95</t>
+          <t>95,98; 98,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96,98; 99,42</t>
+          <t>97,0; 99,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,92; 97,29</t>
+          <t>94,08; 97,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96,57; 98,71</t>
+          <t>96,39; 98,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96,1; 98,64</t>
+          <t>96,15; 98,72</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,22; 96,07</t>
+          <t>89,46; 96,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96,03; 99,33</t>
+          <t>96,03; 99,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97,44; 99,53</t>
+          <t>97,1; 99,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95,12; 98,58</t>
+          <t>94,88; 98,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,76; 99,38</t>
+          <t>95,5; 99,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,54; 97,49</t>
+          <t>94,8; 97,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,99; 97,25</t>
+          <t>93,72; 97,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96,64; 99,07</t>
+          <t>96,53; 99,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96,18; 98,16</t>
+          <t>96,3; 98,17</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>80,74; 83,42</t>
+          <t>80,79; 83,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,45; 83,16</t>
+          <t>80,42; 83,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57,8; 81,59</t>
+          <t>57,56; 81,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,58; 88,89</t>
+          <t>86,6; 88,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86,37; 88,53</t>
+          <t>86,3; 88,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,36; 88,93</t>
+          <t>80,89; 88,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,15; 85,87</t>
+          <t>84,08; 85,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83,85; 85,63</t>
+          <t>83,83; 85,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71,59; 84,8</t>
+          <t>70,31; 84,79</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>197232; 238994</t>
+          <t>197973; 239826</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>205993; 246871</t>
+          <t>206286; 244784</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160454; 231495</t>
+          <t>163638; 235402</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>236493; 277157</t>
+          <t>234889; 276390</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>232890; 272063</t>
+          <t>234566; 270569</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>165021; 208755</t>
+          <t>161806; 208076</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>449152; 507115</t>
+          <t>447061; 506051</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>453343; 509805</t>
+          <t>454388; 508055</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>341615; 425046</t>
+          <t>339931; 424040</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>498581; 541953</t>
+          <t>495451; 541583</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>385508; 428626</t>
+          <t>385517; 430191</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>252539; 301273</t>
+          <t>252991; 301698</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>496091; 532671</t>
+          <t>498604; 533383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>441135; 475778</t>
+          <t>441212; 477357</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>204596; 401392</t>
+          <t>204110; 399294</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1006755; 1065941</t>
+          <t>1007512; 1064829</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>836049; 896777</t>
+          <t>841637; 895833</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>470862; 681433</t>
+          <t>448200; 679334</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>561632; 597038</t>
+          <t>559508; 596278</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>519065; 560475</t>
+          <t>519580; 560497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>389959; 431445</t>
+          <t>392585; 433465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>623833; 656732</t>
+          <t>622931; 655498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>541006; 577640</t>
+          <t>541408; 577005</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>441887; 470782</t>
+          <t>445159; 472082</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1194938; 1245118</t>
+          <t>1193680; 1243122</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1073828; 1124547</t>
+          <t>1069410; 1124267</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>847369; 896964</t>
+          <t>845478; 893535</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>537309; 568814</t>
+          <t>535981; 568483</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>542856; 577258</t>
+          <t>543748; 577403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>245613; 785259</t>
+          <t>237064; 787236</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>539606; 570394</t>
+          <t>538018; 569691</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>571106; 601956</t>
+          <t>571475; 603076</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>642838; 668544</t>
+          <t>643577; 669361</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1088110; 1132247</t>
+          <t>1086508; 1130483</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1124141; 1171910</t>
+          <t>1125200; 1174056</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>729244; 1448902</t>
+          <t>786074; 1448844</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>383641; 404287</t>
+          <t>382570; 404438</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>428027; 452365</t>
+          <t>426946; 451466</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>504974; 528869</t>
+          <t>506000; 529370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>411354; 431237</t>
+          <t>412623; 432128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>451602; 474284</t>
+          <t>452053; 475212</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>509248; 526921</t>
+          <t>509778; 527385</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>804333; 831388</t>
+          <t>803802; 831942</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>886675; 920881</t>
+          <t>882595; 919915</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1022380; 1053954</t>
+          <t>1023759; 1051589</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>288465; 302661</t>
+          <t>287131; 302680</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>319240; 331165</t>
+          <t>318450; 330435</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>344073; 357263</t>
+          <t>344142; 356788</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>327976; 344037</t>
+          <t>327921; 344044</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>361997; 373803</t>
+          <t>362568; 373794</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>589484; 604294</t>
+          <t>589562; 604766</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>621518; 643825</t>
+          <t>622574; 643559</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>687694; 702900</t>
+          <t>686358; 702922</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>937170; 961963</t>
+          <t>937705; 962746</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>219998; 236881</t>
+          <t>220578; 237376</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>245985; 254450</t>
+          <t>246001; 254477</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275517; 281422</t>
+          <t>274556; 281427</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>365591; 378891</t>
+          <t>364673; 378936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>382043; 396509</t>
+          <t>381019; 396471</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>401184; 413716</t>
+          <t>402304; 414010</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>593032; 613611</t>
+          <t>591292; 613765</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>633136; 649050</t>
+          <t>632404; 648544</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>680126; 694098</t>
+          <t>680944; 694141</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2747559; 2838568</t>
+          <t>2749310; 2837390</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2706648; 2797584</t>
+          <t>2705454; 2799000</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1998847; 2821310</t>
+          <t>1990444; 2821953</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3063703; 3145389</t>
+          <t>3064325; 3144046</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3052190; 3128441</t>
+          <t>3049687; 3126251</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2976473; 3253470</t>
+          <t>2959067; 3249668</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5841085; 5960478</t>
+          <t>5836035; 5956632</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5783798; 5906573</t>
+          <t>5782206; 5902103</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5094912; 6034595</t>
+          <t>5003784; 6034223</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38B-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>43,96; 53,25</t>
+          <t>43,67; 52,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,81; 60,29</t>
+          <t>50,46; 60,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,91; 58,85</t>
+          <t>37,84; 53,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,22; 64,98</t>
+          <t>55,97; 65,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,56; 68,71</t>
+          <t>59,78; 69,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,84; 66,67</t>
+          <t>51,08; 65,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,05; 57,79</t>
+          <t>51,17; 57,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,81; 63,52</t>
+          <t>56,36; 63,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,74; 59,55</t>
+          <t>46,09; 56,91</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>70,14%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,71; 79,47</t>
+          <t>73,15; 79,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,4; 72,98</t>
+          <t>65,2; 72,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,73; 71,23</t>
+          <t>58,46; 70,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,13; 87,86</t>
+          <t>82,12; 87,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,29; 84,71</t>
+          <t>78,3; 84,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,9; 78,06</t>
+          <t>71,44; 79,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,19; 82,64</t>
+          <t>78,04; 82,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72,99; 77,69</t>
+          <t>72,6; 77,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,93; 72,65</t>
+          <t>66,62; 73,96</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,4; 87,81</t>
+          <t>82,73; 87,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,55; 84,74</t>
+          <t>78,68; 84,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,2; 80,82</t>
+          <t>71,19; 78,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,76; 92,35</t>
+          <t>87,63; 92,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,67; 88,11</t>
+          <t>82,4; 87,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,09; 87,05</t>
+          <t>81,13; 86,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,95; 89,51</t>
+          <t>85,94; 89,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,24; 85,41</t>
+          <t>81,61; 85,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78,38; 82,84</t>
+          <t>76,86; 81,57</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,35; 92,65</t>
+          <t>87,83; 92,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,11; 90,38</t>
+          <t>85,03; 90,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,7; 88,67</t>
+          <t>85,06; 90,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,74; 92,91</t>
+          <t>88,11; 92,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,04; 92,91</t>
+          <t>88,13; 92,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,35; 93,97</t>
+          <t>89,33; 92,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,57; 92,15</t>
+          <t>88,77; 92,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,36; 91,16</t>
+          <t>87,44; 91,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,13; 90,55</t>
+          <t>87,89; 91,02</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,23; 95,39</t>
+          <t>90,33; 95,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89,33; 94,47</t>
+          <t>89,46; 94,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,32; 94,49</t>
+          <t>89,15; 93,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92,78; 97,17</t>
+          <t>92,61; 96,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,2; 95,88</t>
+          <t>90,69; 95,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,04; 96,25</t>
+          <t>93,68; 96,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,53; 95,77</t>
+          <t>92,53; 95,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>90,66; 94,49</t>
+          <t>91,31; 94,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,39; 94,9</t>
+          <t>92,0; 94,7</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,29; 98,35</t>
+          <t>92,87; 98,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,25; 98,83</t>
+          <t>95,52; 99,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,67; 97,11</t>
+          <t>93,26; 96,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92,63; 97,19</t>
+          <t>92,51; 97,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>95,98; 98,95</t>
+          <t>95,97; 98,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>97,0; 99,5</t>
+          <t>96,01; 98,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94,08; 97,25</t>
+          <t>93,89; 97,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>96,39; 98,71</t>
+          <t>96,55; 98,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96,15; 98,72</t>
+          <t>95,22; 97,38</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,46; 96,27</t>
+          <t>88,69; 96,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96,03; 99,34</t>
+          <t>96,01; 99,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97,1; 99,53</t>
+          <t>97,21; 99,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94,88; 98,59</t>
+          <t>94,87; 98,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,5; 99,38</t>
+          <t>95,61; 99,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,8; 97,56</t>
+          <t>94,58; 97,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,72; 97,28</t>
+          <t>93,79; 97,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96,53; 99,0</t>
+          <t>96,6; 99,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96,3; 98,17</t>
+          <t>96,07; 98,12</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>80,79; 83,38</t>
+          <t>80,77; 83,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,42; 83,2</t>
+          <t>80,48; 83,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57,56; 81,61</t>
+          <t>78,27; 81,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,6; 88,85</t>
+          <t>86,55; 88,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86,3; 88,47</t>
+          <t>86,23; 88,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,89; 88,83</t>
+          <t>85,51; 87,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,08; 85,81</t>
+          <t>84,18; 85,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83,83; 85,56</t>
+          <t>83,79; 85,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,31; 84,79</t>
+          <t>82,29; 84,51</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196476</t>
+          <t>184074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>186502</t>
+          <t>211555</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>382977</t>
+          <t>395629</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>197973; 239826</t>
+          <t>196691; 238640</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>206286; 244784</t>
+          <t>204842; 246121</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163638; 235402</t>
+          <t>154311; 220169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234889; 276390</t>
+          <t>238055; 278081</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>234566; 270569</t>
+          <t>235402; 271862</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>161806; 208076</t>
+          <t>184566; 237170</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>447061; 506051</t>
+          <t>448126; 506855</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>454388; 508055</t>
+          <t>450767; 508663</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>339931; 424040</t>
+          <t>354501; 437744</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278585</t>
+          <t>307623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>340451</t>
+          <t>378309</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>619036</t>
+          <t>685933</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>495451; 541583</t>
+          <t>498466; 541362</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>385517; 430191</t>
+          <t>384326; 430083</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>252991; 301698</t>
+          <t>278793; 334959</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>498604; 533383</t>
+          <t>498539; 532257</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>441212; 477357</t>
+          <t>441246; 476749</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>204110; 399294</t>
+          <t>357983; 398068</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1007512; 1064829</t>
+          <t>1005595; 1066090</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>841637; 895833</t>
+          <t>837127; 895168</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>448200; 679334</t>
+          <t>651543; 723315</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413864</t>
+          <t>464456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>457912</t>
+          <t>521292</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>871777</t>
+          <t>985748</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>559508; 596278</t>
+          <t>561741; 596571</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>519580; 560497</t>
+          <t>520402; 560433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>392585; 433465</t>
+          <t>441970; 486801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>622931; 655498</t>
+          <t>621981; 655200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>541408; 577005</t>
+          <t>539631; 576220</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>445159; 472082</t>
+          <t>504081; 539055</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1193680; 1243122</t>
+          <t>1193578; 1241396</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1069410; 1124267</t>
+          <t>1074276; 1127295</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>845478; 893535</t>
+          <t>954708; 1013208</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>562546</t>
+          <t>614582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>656379</t>
+          <t>670253</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1218924</t>
+          <t>1284836</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>535981; 568483</t>
+          <t>538941; 567673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>543748; 577403</t>
+          <t>543234; 577483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>237064; 787236</t>
+          <t>595943; 631029</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>538018; 569691</t>
+          <t>540292; 569724</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>571475; 603076</t>
+          <t>572056; 602906</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>643577; 669361</t>
+          <t>657256; 683189</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1086508; 1130483</t>
+          <t>1088978; 1130757</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1125200; 1174056</t>
+          <t>1126245; 1172971</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>786074; 1448844</t>
+          <t>1262473; 1307371</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>518999</t>
+          <t>558427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>520010</t>
+          <t>579642</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1039010</t>
+          <t>1138069</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>382570; 404438</t>
+          <t>383012; 404325</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>426946; 451466</t>
+          <t>427524; 451962</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>506000; 529370</t>
+          <t>542377; 569920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>412623; 432128</t>
+          <t>411858; 431241</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>452053; 475212</t>
+          <t>449530; 474763</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>509778; 527385</t>
+          <t>570395; 587255</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>803802; 831942</t>
+          <t>803835; 832025</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>882595; 919915</t>
+          <t>888994; 920217</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1023759; 1051589</t>
+          <t>1119809; 1152721</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>351548</t>
+          <t>387382</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>597536</t>
+          <t>427014</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>949083</t>
+          <t>814396</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>287131; 302680</t>
+          <t>285814; 302595</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>318450; 330435</t>
+          <t>319364; 330974</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>344142; 356788</t>
+          <t>378699; 393616</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>327921; 344044</t>
+          <t>327472; 344013</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>362568; 373794</t>
+          <t>362537; 373892</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>589562; 604766</t>
+          <t>421054; 431231</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>622574; 643559</t>
+          <t>621355; 643830</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>686358; 702922</t>
+          <t>687498; 702701</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>937705; 962746</t>
+          <t>804279; 822532</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>279227</t>
+          <t>306248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>409014</t>
+          <t>445709</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>688241</t>
+          <t>751956</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>220578; 237376</t>
+          <t>218684; 237428</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>246001; 254477</t>
+          <t>245937; 254401</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>274556; 281427</t>
+          <t>301554; 308756</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>364673; 378936</t>
+          <t>364651; 378836</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>381019; 396471</t>
+          <t>381451; 396416</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>402304; 414010</t>
+          <t>437889; 451795</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>591292; 613765</t>
+          <t>591776; 613003</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>632404; 648544</t>
+          <t>632820; 649058</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>680944; 694141</t>
+          <t>742775; 758620</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2601246</t>
+          <t>2822793</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3167804</t>
+          <t>3233776</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5769048</t>
+          <t>6056569</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2749310; 2837390</t>
+          <t>2748463; 2839886</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2705454; 2799000</t>
+          <t>2707488; 2797267</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1990444; 2821953</t>
+          <t>2763611; 2884715</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3064325; 3144046</t>
+          <t>3062664; 3142480</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3049687; 3126251</t>
+          <t>3046994; 3125537</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2959067; 3249668</t>
+          <t>3189397; 3278648</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5836035; 5956632</t>
+          <t>5843356; 5955221</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5782206; 5902103</t>
+          <t>5779928; 5893636</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5003784; 6034223</t>
+          <t>5974747; 6136083</t>
         </is>
       </c>
     </row>
